--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -27926,6 +27926,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1199">
+      <c r="A1199" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B1199" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1199" t="n">
+        <v>0.966000020503998</v>
+      </c>
+      <c r="D1199" t="n">
+        <v>0.966000020503998</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>0.966000020503998</v>
+      </c>
+      <c r="F1199" t="n">
+        <v>0.966000020503998</v>
+      </c>
+      <c r="G1199" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -27949,6 +27949,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1200">
+      <c r="A1200" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1200" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1200" t="n">
+        <v>0.966000020503998</v>
+      </c>
+      <c r="D1200" t="n">
+        <v>0.966000020503998</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>0.966000020503998</v>
+      </c>
+      <c r="F1200" t="n">
+        <v>0.966000020503998</v>
+      </c>
+      <c r="G1200" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1201" t="n">
+        <v>40</v>
+      </c>
+      <c r="C1201" t="n">
+        <v>0.986000001430511</v>
+      </c>
+      <c r="D1201" t="n">
+        <v>0.967999994754791</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>0.967999994754791</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>0.986000001430511</v>
+      </c>
+      <c r="G1201" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -27995,6 +27995,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1202">
+      <c r="A1202" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1202" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1202" t="n">
+        <v>0.986000001430511</v>
+      </c>
+      <c r="D1202" t="n">
+        <v>0.986000001430511</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>0.986000001430511</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>0.986000001430511</v>
+      </c>
+      <c r="G1202" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1203" t="n">
+        <v>5120</v>
+      </c>
+      <c r="C1203" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="G1203" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -27859,22 +27859,22 @@
     </row>
     <row r="1196">
       <c r="A1196" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1196" t="n">
-        <v>1705</v>
+        <v>0</v>
       </c>
       <c r="C1196" t="n">
-        <v>0.977999985218048</v>
+        <v>0.967999994754791</v>
       </c>
       <c r="D1196" t="n">
-        <v>0.917999982833862</v>
+        <v>0.967999994754791</v>
       </c>
       <c r="E1196" t="n">
-        <v>0.927999973297119</v>
+        <v>0.967999994754791</v>
       </c>
       <c r="F1196" t="n">
-        <v>0.977999985218048</v>
+        <v>0.967999994754791</v>
       </c>
       <c r="G1196" t="s">
         <v>7</v>
@@ -27882,22 +27882,22 @@
     </row>
     <row r="1197">
       <c r="A1197" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1197" t="n">
-        <v>5000</v>
+        <v>1705</v>
       </c>
       <c r="C1197" t="n">
-        <v>0.970000028610229</v>
+        <v>0.977999985218048</v>
       </c>
       <c r="D1197" t="n">
-        <v>0.970000028610229</v>
+        <v>0.917999982833862</v>
       </c>
       <c r="E1197" t="n">
-        <v>0.970000028610229</v>
+        <v>0.927999973297119</v>
       </c>
       <c r="F1197" t="n">
-        <v>0.970000028610229</v>
+        <v>0.977999985218048</v>
       </c>
       <c r="G1197" t="s">
         <v>7</v>
@@ -27905,22 +27905,22 @@
     </row>
     <row r="1198">
       <c r="A1198" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1198" t="n">
-        <v>72</v>
+        <v>5000</v>
       </c>
       <c r="C1198" t="n">
-        <v>0.966000020503998</v>
+        <v>0.970000028610229</v>
       </c>
       <c r="D1198" t="n">
-        <v>0.927999973297119</v>
+        <v>0.970000028610229</v>
       </c>
       <c r="E1198" t="n">
-        <v>0.927999973297119</v>
+        <v>0.970000028610229</v>
       </c>
       <c r="F1198" t="n">
-        <v>0.966000020503998</v>
+        <v>0.970000028610229</v>
       </c>
       <c r="G1198" t="s">
         <v>7</v>
@@ -27928,19 +27928,19 @@
     </row>
     <row r="1199">
       <c r="A1199" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1199" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="C1199" t="n">
         <v>0.966000020503998</v>
       </c>
       <c r="D1199" t="n">
-        <v>0.966000020503998</v>
+        <v>0.927999973297119</v>
       </c>
       <c r="E1199" t="n">
-        <v>0.966000020503998</v>
+        <v>0.927999973297119</v>
       </c>
       <c r="F1199" t="n">
         <v>0.966000020503998</v>
@@ -27951,7 +27951,7 @@
     </row>
     <row r="1200">
       <c r="A1200" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1200" t="n">
         <v>0</v>
@@ -27974,22 +27974,22 @@
     </row>
     <row r="1201">
       <c r="A1201" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1201" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C1201" t="n">
-        <v>0.986000001430511</v>
+        <v>0.966000020503998</v>
       </c>
       <c r="D1201" t="n">
-        <v>0.967999994754791</v>
+        <v>0.966000020503998</v>
       </c>
       <c r="E1201" t="n">
-        <v>0.967999994754791</v>
+        <v>0.966000020503998</v>
       </c>
       <c r="F1201" t="n">
-        <v>0.986000001430511</v>
+        <v>0.966000020503998</v>
       </c>
       <c r="G1201" t="s">
         <v>7</v>
@@ -27997,19 +27997,19 @@
     </row>
     <row r="1202">
       <c r="A1202" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1202" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C1202" t="n">
         <v>0.986000001430511</v>
       </c>
       <c r="D1202" t="n">
-        <v>0.986000001430511</v>
+        <v>0.967999994754791</v>
       </c>
       <c r="E1202" t="n">
-        <v>0.986000001430511</v>
+        <v>0.967999994754791</v>
       </c>
       <c r="F1202" t="n">
         <v>0.986000001430511</v>
@@ -28020,24 +28020,47 @@
     </row>
     <row r="1203">
       <c r="A1203" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1203" t="n">
-        <v>5120</v>
+        <v>0</v>
       </c>
       <c r="C1203" t="n">
+        <v>0.986000001430511</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>0.986000001430511</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>0.986000001430511</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>0.986000001430511</v>
+      </c>
+      <c r="G1203" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1204" t="n">
+        <v>472</v>
+      </c>
+      <c r="C1204" t="n">
         <v>0.959999978542328</v>
       </c>
-      <c r="D1203" t="n">
-        <v>0.899999976158142</v>
-      </c>
-      <c r="E1203" t="n">
-        <v>0.939999997615814</v>
-      </c>
-      <c r="F1203" t="n">
-        <v>0.939999997615814</v>
-      </c>
-      <c r="G1203" t="s">
+      <c r="D1204" t="n">
+        <v>0.912000000476837</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>0.952000021934509</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="G1204" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -28043,24 +28043,47 @@
     </row>
     <row r="1204">
       <c r="A1204" s="1" t="n">
-        <v>46283.2916666667</v>
+        <v>46282.2916666667</v>
       </c>
       <c r="B1204" t="n">
-        <v>472</v>
+        <v>5120</v>
       </c>
       <c r="C1204" t="n">
         <v>0.959999978542328</v>
       </c>
       <c r="D1204" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="G1204" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1205" t="n">
+        <v>472</v>
+      </c>
+      <c r="C1205" t="n">
+        <v>0.959999978542328</v>
+      </c>
+      <c r="D1205" t="n">
         <v>0.912000000476837</v>
       </c>
-      <c r="E1204" t="n">
+      <c r="E1205" t="n">
         <v>0.952000021934509</v>
       </c>
-      <c r="F1204" t="n">
+      <c r="F1205" t="n">
         <v>0.959999978542328</v>
       </c>
-      <c r="G1204" t="s">
+      <c r="G1205" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -31757,6 +31757,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1208">
+      <c r="A1208" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1208" t="n">
+        <v>2031</v>
+      </c>
+      <c r="C1208" t="n">
+        <v>0.907999992370605</v>
+      </c>
+      <c r="D1208" t="n">
+        <v>0.864000022411346</v>
+      </c>
+      <c r="E1208" t="n">
+        <v>0.878000020980835</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>0.907999992370605</v>
+      </c>
+      <c r="G1208" t="n">
+        <v>0.907999992370605</v>
+      </c>
+      <c r="H1208" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -31783,6 +31783,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1209">
+      <c r="A1209" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1209" t="n">
+        <v>6150</v>
+      </c>
+      <c r="C1209" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="D1209" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="E1209" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="F1209" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="G1209" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="H1209" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -31809,6 +31809,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1210">
+      <c r="A1210" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1210" t="n">
+        <v>530</v>
+      </c>
+      <c r="C1210" t="n">
+        <v>0.945999979972839</v>
+      </c>
+      <c r="D1210" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="E1210" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="F1210" t="n">
+        <v>0.945999979972839</v>
+      </c>
+      <c r="G1210" t="n">
+        <v>0.945999979972839</v>
+      </c>
+      <c r="H1210" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -31887,6 +31887,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1213">
+      <c r="A1213" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1213" t="n">
+        <v>9070</v>
+      </c>
+      <c r="C1213" t="n">
+        <v>0.939999997615814</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>0.879999995231628</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>0.924000024795532</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="G1213" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="H1213" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -28333,8 +28333,31 @@
       <c r="E1216" t="n">
         <v>0.888000011444092</v>
       </c>
-      <c r="F1216"/>
+      <c r="F1216" t="n">
+        <v>0.898000001907349</v>
+      </c>
       <c r="G1216" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1217" t="n">
+        <v>49</v>
+      </c>
+      <c r="C1217" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="D1217" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="F1217"/>
+      <c r="G1217" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -28356,7 +28356,9 @@
       <c r="E1217" t="n">
         <v>0.889999985694885</v>
       </c>
-      <c r="F1217"/>
+      <c r="F1217" t="n">
+        <v>0.889999985694885</v>
+      </c>
       <c r="G1217" t="s">
         <v>7</v>
       </c>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -28363,6 +28363,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1218">
+      <c r="A1218" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1218" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1218" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="F1218" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="G1218" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1219" t="n">
+        <v>4555</v>
+      </c>
+      <c r="C1219" t="n">
+        <v>0.898000001907349</v>
+      </c>
+      <c r="D1219" t="n">
+        <v>0.88400000333786</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>0.88400000333786</v>
+      </c>
+      <c r="F1219"/>
+      <c r="G1219" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -28402,8 +28402,31 @@
       <c r="E1219" t="n">
         <v>0.88400000333786</v>
       </c>
-      <c r="F1219"/>
+      <c r="F1219" t="n">
+        <v>0.898000001907349</v>
+      </c>
       <c r="G1219" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1220" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1220" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="F1220"/>
+      <c r="G1220" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -28432,6 +28432,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1221">
+      <c r="A1221" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1221" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1221" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="G1221" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -28501,6 +28501,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1224">
+      <c r="A1224" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1224" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1224" t="n">
+        <v>0.903999984264374</v>
+      </c>
+      <c r="D1224" t="n">
+        <v>0.903999984264374</v>
+      </c>
+      <c r="E1224" t="n">
+        <v>0.903999984264374</v>
+      </c>
+      <c r="F1224" t="n">
+        <v>0.903999984264374</v>
+      </c>
+      <c r="G1224" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -35903,6 +35903,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1226">
+      <c r="A1226" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1226" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1226" t="n">
+        <v>0.903999984264374</v>
+      </c>
+      <c r="D1226" t="n">
+        <v>0.903999984264374</v>
+      </c>
+      <c r="E1226" t="n">
+        <v>0.903999984264374</v>
+      </c>
+      <c r="F1226" t="n">
+        <v>0.903999984264374</v>
+      </c>
+      <c r="G1226" t="n">
+        <v>0.903999984264374</v>
+      </c>
+      <c r="H1226" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1226" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1227" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1227" t="n">
+        <v>0.90200001001358</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>0.90200001001358</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>0.867999970912933</v>
+      </c>
+      <c r="F1227" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="G1227" t="n">
+        <v>0.889999985694885</v>
+      </c>
+      <c r="H1227" t="n">
+        <v>520</v>
+      </c>
+      <c r="I1227" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -35961,6 +35961,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1228" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1228" t="n">
+        <v>0.864000022411346</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>0.864000022411346</v>
+      </c>
+      <c r="F1228" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="G1228" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="H1228" t="n">
+        <v>400</v>
+      </c>
+      <c r="I1228" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -35990,6 +35990,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1229">
+      <c r="A1229" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1229" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1229" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>0.896000027656555</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>0.903999984264374</v>
+      </c>
+      <c r="G1229" t="n">
+        <v>0.903999984264374</v>
+      </c>
+      <c r="H1229" t="n">
+        <v>9220</v>
+      </c>
+      <c r="I1229" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -36001,7 +36001,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="D1229" t="n">
-        <v>0.896000027656555</v>
+        <v>0.903999984264374</v>
       </c>
       <c r="E1229" t="n">
         <v>0.870000004768372</v>
@@ -36016,6 +36016,35 @@
         <v>9220</v>
       </c>
       <c r="I1229" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1230" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1230" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="D1230" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="E1230" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="F1230" t="n">
+        <v>0.90200001001358</v>
+      </c>
+      <c r="G1230" t="n">
+        <v>0.90200001001358</v>
+      </c>
+      <c r="H1230" t="n">
+        <v>320</v>
+      </c>
+      <c r="I1230" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -36030,7 +36030,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="D1230" t="n">
-        <v>0.899999976158142</v>
+        <v>0.90200001001358</v>
       </c>
       <c r="E1230" t="n">
         <v>0.870000004768372</v>
@@ -36045,6 +36045,35 @@
         <v>320</v>
       </c>
       <c r="I1230" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1231" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1231" t="n">
+        <v>0.874000012874603</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>0.903999984264374</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="G1231" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="H1231" t="n">
+        <v>2030</v>
+      </c>
+      <c r="I1231" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -36077,6 +36077,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1232">
+      <c r="A1232" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1232" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1232" t="n">
+        <v>0.870000004768372</v>
+      </c>
+      <c r="D1232" t="n">
+        <v>0.898000001907349</v>
+      </c>
+      <c r="E1232" t="n">
+        <v>0.861999988555908</v>
+      </c>
+      <c r="F1232" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="G1232" t="n">
+        <v>0.899999976158142</v>
+      </c>
+      <c r="H1232" t="n">
+        <v>16450</v>
+      </c>
+      <c r="I1232" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -36088,7 +36088,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="D1232" t="n">
-        <v>0.898000001907349</v>
+        <v>0.899999976158142</v>
       </c>
       <c r="E1232" t="n">
         <v>0.861999988555908</v>
@@ -36103,6 +36103,35 @@
         <v>16450</v>
       </c>
       <c r="I1232" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1233" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1233" t="n">
+        <v>0.907999992370605</v>
+      </c>
+      <c r="D1233" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="E1233" t="n">
+        <v>0.907999992370605</v>
+      </c>
+      <c r="F1233" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="G1233" t="n">
+        <v>0.920000016689301</v>
+      </c>
+      <c r="H1233" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1233" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -36135,6 +36135,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1234">
+      <c r="A1234" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1234" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1234" t="n">
+        <v>0.874000012874603</v>
+      </c>
+      <c r="D1234" t="n">
+        <v>0.874000012874603</v>
+      </c>
+      <c r="E1234" t="n">
+        <v>0.86599999666214</v>
+      </c>
+      <c r="F1234" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="G1234" t="n">
+        <v>0.860000014305115</v>
+      </c>
+      <c r="H1234" t="n">
+        <v>9287</v>
+      </c>
+      <c r="I1234" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ISC.MI.xlsx
+++ b/data/ISC.MI.xlsx
@@ -36149,7 +36149,7 @@
         <v>0.874000012874603</v>
       </c>
       <c r="E1234" t="n">
-        <v>0.86599999666214</v>
+        <v>0.860000014305115</v>
       </c>
       <c r="F1234" t="n">
         <v>0.860000014305115</v>
@@ -36161,6 +36161,35 @@
         <v>9287</v>
       </c>
       <c r="I1234" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1235" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1235" t="n">
+        <v>0.874000012874603</v>
+      </c>
+      <c r="D1235" t="n">
+        <v>0.917999982833862</v>
+      </c>
+      <c r="E1235" t="n">
+        <v>0.874000012874603</v>
+      </c>
+      <c r="F1235" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="G1235" t="n">
+        <v>0.949999988079071</v>
+      </c>
+      <c r="H1235" t="n">
+        <v>16994</v>
+      </c>
+      <c r="I1235" t="s">
         <v>9</v>
       </c>
     </row>
